--- a/output/graficos_dimensiones/comunal_d_depmay_a_2019_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2019_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:09</t>
+    <t xml:space="preserve">2026-09-10 01:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmay_a_2019_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2019_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:22</t>
+    <t xml:space="preserve">2026-09-12 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmay_a_2019_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2019_o higgins.xlsx
@@ -60,6 +60,9 @@
     <t xml:space="preserve">Litueche</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pichidegua</t>
   </si>
   <si>
@@ -132,9 +135,6 @@
     <t xml:space="preserve">Machalí</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:34</t>
+    <t xml:space="preserve">2026-09-24 00:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -710,13 +710,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6113</v>
+        <v>6204</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>32.79</v>
+        <v>33.63</v>
       </c>
     </row>
     <row r="11">
@@ -727,13 +727,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6307</v>
+        <v>6113</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>32.2</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="12">
@@ -744,13 +744,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6306</v>
+        <v>6307</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>32.11</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="13">
@@ -761,13 +761,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6117</v>
+        <v>6306</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>32.07</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="14">
@@ -778,13 +778,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6109</v>
+        <v>6117</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>31.95</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="15">
@@ -795,13 +795,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6104</v>
+        <v>6109</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>31.1</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="16">
@@ -812,13 +812,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6112</v>
+        <v>6104</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>30.44</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6308</v>
+        <v>6112</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>30.31</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="18">
@@ -846,13 +846,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6305</v>
+        <v>6308</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>30.01</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="19">
@@ -863,13 +863,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6107</v>
+        <v>6305</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
     </row>
     <row r="20">
@@ -880,13 +880,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6114</v>
+        <v>6107</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>29.24</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="21">
@@ -897,13 +897,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6105</v>
+        <v>6114</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>28.76</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="22">
@@ -914,13 +914,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6310</v>
+        <v>6105</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>28.74</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="23">
@@ -931,13 +931,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6201</v>
+        <v>6310</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>28.39</v>
+        <v>28.74</v>
       </c>
     </row>
     <row r="24">
@@ -948,13 +948,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6303</v>
+        <v>6201</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.19</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="25">
@@ -965,13 +965,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6102</v>
+        <v>6303</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>27.23</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="26">
@@ -982,13 +982,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6110</v>
+        <v>6102</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>27.15</v>
+        <v>27.23</v>
       </c>
     </row>
     <row r="27">
@@ -999,13 +999,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6111</v>
+        <v>6110</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>27.1</v>
+        <v>27.15</v>
       </c>
     </row>
     <row r="28">
@@ -1016,13 +1016,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6115</v>
+        <v>6111</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>26.95</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="29">
@@ -1033,13 +1033,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6301</v>
+        <v>6115</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>26.55</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="30">
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6101</v>
+        <v>6301</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>26.13</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="31">
@@ -1067,13 +1067,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6106</v>
+        <v>6101</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>24.14</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="32">
@@ -1084,13 +1084,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6116</v>
+        <v>6106</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>23.86</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="33">
@@ -1101,13 +1101,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6108</v>
+        <v>6116</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>21.31</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="34">
@@ -1118,10 +1118,14 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6204</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+        <v>6108</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>21.31</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E34"/>
